--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,439 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120173739</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>292480</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6521913</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120174574</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>292510</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6521818</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120173772</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79567</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>292480</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6521913</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120173709</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56522</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>292402</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6521878</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173739</v>
+        <v>120174574</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,35 +926,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>292480</v>
+        <v>292510</v>
       </c>
       <c r="R4" t="n">
-        <v>6521913</v>
+        <v>6521818</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,6 +1006,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120174574</v>
+        <v>120173769</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,35 +1037,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>292510</v>
+        <v>292480</v>
       </c>
       <c r="R5" t="n">
-        <v>6521818</v>
+        <v>6521913</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,7 +1117,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120173772</v>
+        <v>120173709</v>
       </c>
       <c r="B6" t="n">
-        <v>79567</v>
+        <v>56522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,26 +1151,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292480</v>
+        <v>292402</v>
       </c>
       <c r="R6" t="n">
-        <v>6521913</v>
+        <v>6521878</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,7 +1223,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173709</v>
+        <v>120173772</v>
       </c>
       <c r="B7" t="n">
-        <v>56522</v>
+        <v>79567</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,27 +1257,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>292402</v>
+        <v>292480</v>
       </c>
       <c r="R7" t="n">
-        <v>6521878</v>
+        <v>6521913</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,6 +1328,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,6 +1345,1109 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120279004</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Amunderöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>292460</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521909</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>endast läte</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120278936</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90546</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Amunderöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>292494</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6521833</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120278950</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mårtensröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>292486</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6521810</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120279010</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Amunderöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>292451</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6521897</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sönderhackad död gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120279012</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Amunderöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>292451</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6521897</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120279013</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Amunderöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>292553</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6521837</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120279026</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90546</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Amunderöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>292459</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6521917</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer på döende Asp</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120279002</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>amunderöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>292480</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6521807</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>massor av hack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120278951</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mårtensröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>292480</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6521806</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119764981</v>
       </c>
       <c r="B2" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>119871405</v>
       </c>
       <c r="B3" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120174574</v>
+        <v>120173709</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,35 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>292510</v>
+        <v>292402</v>
       </c>
       <c r="R4" t="n">
-        <v>6521818</v>
+        <v>6521878</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,7 +1002,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120173769</v>
+        <v>120174574</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,35 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>292480</v>
+        <v>292510</v>
       </c>
       <c r="R5" t="n">
-        <v>6521913</v>
+        <v>6521818</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120173709</v>
+        <v>120173769</v>
       </c>
       <c r="B6" t="n">
-        <v>56522</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,31 +1143,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292402</v>
+        <v>292480</v>
       </c>
       <c r="R6" t="n">
-        <v>6521878</v>
+        <v>6521913</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,7 +1244,7 @@
         <v>120173772</v>
       </c>
       <c r="B7" t="n">
-        <v>79567</v>
+        <v>79583</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120279004</v>
+        <v>120278936</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>90564</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,35 +1359,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1390,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292460</v>
+        <v>292494</v>
       </c>
       <c r="R8" t="n">
-        <v>6521909</v>
+        <v>6521833</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,12 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>endast läte</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,6 +1444,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120278936</v>
+        <v>120279010</v>
       </c>
       <c r="B9" t="n">
-        <v>90546</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,30 +1475,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4660</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1515,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292494</v>
+        <v>292451</v>
       </c>
       <c r="R9" t="n">
-        <v>6521833</v>
+        <v>6521897</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1550,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sönderhackad död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1570,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>120278950</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120279010</v>
+        <v>120279004</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,26 +1725,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292451</v>
+        <v>292460</v>
       </c>
       <c r="R11" t="n">
-        <v>6521897</v>
+        <v>6521909</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sönderhackad död gran</t>
+          <t>endast läte</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120279012</v>
+        <v>120279002</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,48 +1846,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292451</v>
+        <v>292480</v>
       </c>
       <c r="R12" t="n">
-        <v>6521897</v>
+        <v>6521807</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1916,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1926,7 +1927,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>massor av hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,7 +1941,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1957,7 +1962,7 @@
         <v>120279013</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2079,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120279026</v>
+        <v>120279012</v>
       </c>
       <c r="B14" t="n">
-        <v>90546</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,34 +2096,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2126,10 +2131,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292459</v>
+        <v>292451</v>
       </c>
       <c r="R14" t="n">
-        <v>6521917</v>
+        <v>6521897</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2161,7 +2166,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,12 +2176,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer på döende Asp</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2204,10 +2204,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120279002</v>
+        <v>120278951</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,49 +2216,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>292480</v>
       </c>
       <c r="R15" t="n">
-        <v>6521807</v>
+        <v>6521806</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>massor av hack</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,6 +2306,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2329,10 +2325,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120278951</v>
+        <v>120279026</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>90564</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,46 +2337,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292480</v>
+        <v>292459</v>
       </c>
       <c r="R16" t="n">
-        <v>6521806</v>
+        <v>6521917</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2412,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2422,7 +2417,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på döende Asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120279004</v>
+        <v>120279002</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,26 +1725,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1753,17 +1753,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292460</v>
+        <v>292480</v>
       </c>
       <c r="R11" t="n">
-        <v>6521909</v>
+        <v>6521807</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>endast läte</t>
+          <t>massor av hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120279002</v>
+        <v>120279013</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1878,14 +1878,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292480</v>
+        <v>292553</v>
       </c>
       <c r="R12" t="n">
-        <v>6521807</v>
+        <v>6521837</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>massor av hack</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120279013</v>
+        <v>120279004</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,26 +1975,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292553</v>
+        <v>292460</v>
       </c>
       <c r="R13" t="n">
-        <v>6521837</v>
+        <v>6521909</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>endast läte</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173709</v>
+        <v>120173769</v>
       </c>
       <c r="B4" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,31 +926,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>292402</v>
+        <v>292480</v>
       </c>
       <c r="R4" t="n">
-        <v>6521878</v>
+        <v>6521913</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120174574</v>
+        <v>120173772</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>79583</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1036,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>292510</v>
+        <v>292480</v>
       </c>
       <c r="R5" t="n">
-        <v>6521818</v>
+        <v>6521913</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1131,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120173769</v>
+        <v>120174574</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,35 +1142,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1179,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292480</v>
+        <v>292510</v>
       </c>
       <c r="R6" t="n">
-        <v>6521913</v>
+        <v>6521818</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,6 +1222,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173772</v>
+        <v>120173709</v>
       </c>
       <c r="B7" t="n">
-        <v>79583</v>
+        <v>56532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,26 +1257,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>292480</v>
+        <v>292402</v>
       </c>
       <c r="R7" t="n">
-        <v>6521913</v>
+        <v>6521878</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120278936</v>
+        <v>120279013</v>
       </c>
       <c r="B8" t="n">
-        <v>90564</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,30 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1390,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292494</v>
+        <v>292553</v>
       </c>
       <c r="R8" t="n">
-        <v>6521833</v>
+        <v>6521837</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1440,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,7 +1454,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1463,7 +1472,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120279010</v>
+        <v>120279002</v>
       </c>
       <c r="B9" t="n">
         <v>57336</v>
@@ -1507,17 +1516,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292451</v>
+        <v>292480</v>
       </c>
       <c r="R9" t="n">
-        <v>6521897</v>
+        <v>6521807</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1565,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sönderhackad död gran</t>
+          <t>massor av hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,7 +1597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120278950</v>
+        <v>120279012</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1623,23 +1632,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292486</v>
+        <v>292451</v>
       </c>
       <c r="R10" t="n">
-        <v>6521810</v>
+        <v>6521897</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1709,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120279002</v>
+        <v>120279004</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,26 +1733,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1753,17 +1761,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292480</v>
+        <v>292460</v>
       </c>
       <c r="R11" t="n">
-        <v>6521807</v>
+        <v>6521909</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,12 +1810,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>massor av hack</t>
+          <t>endast läte</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120279013</v>
+        <v>120278951</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,49 +1854,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292553</v>
+        <v>292480</v>
       </c>
       <c r="R12" t="n">
-        <v>6521837</v>
+        <v>6521806</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1917,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,12 +1935,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,6 +1944,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120279004</v>
+        <v>120278936</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>90564</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,35 +1975,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>4660</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2007,13 +2006,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292460</v>
+        <v>292494</v>
       </c>
       <c r="R13" t="n">
-        <v>6521909</v>
+        <v>6521833</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2042,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,12 +2051,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>endast läte</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,6 +2060,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2084,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120279012</v>
+        <v>120279026</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>90564</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,34 +2091,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2131,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292451</v>
+        <v>292459</v>
       </c>
       <c r="R14" t="n">
-        <v>6521897</v>
+        <v>6521917</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2166,7 +2161,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,7 +2171,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer på döende Asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2204,7 +2204,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120278951</v>
+        <v>120278950</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292480</v>
+        <v>292486</v>
       </c>
       <c r="R15" t="n">
-        <v>6521806</v>
+        <v>6521810</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120279026</v>
+        <v>120279010</v>
       </c>
       <c r="B16" t="n">
-        <v>90564</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,34 +2337,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4660</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2372,10 +2373,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292459</v>
+        <v>292451</v>
       </c>
       <c r="R16" t="n">
-        <v>6521917</v>
+        <v>6521897</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2422,7 +2423,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer på döende Asp</t>
+          <t>sönderhackad död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,9 +2432,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173769</v>
+        <v>120173739</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -952,7 +952,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120174574</v>
+        <v>120173709</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,35 +1142,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292510</v>
+        <v>292402</v>
       </c>
       <c r="R6" t="n">
-        <v>6521818</v>
+        <v>6521878</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1241,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173709</v>
+        <v>120174574</v>
       </c>
       <c r="B7" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,31 +1248,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>292402</v>
+        <v>292510</v>
       </c>
       <c r="R7" t="n">
-        <v>6521878</v>
+        <v>6521818</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,6 +1328,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120279013</v>
+        <v>120279004</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,26 +1363,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292553</v>
+        <v>292460</v>
       </c>
       <c r="R8" t="n">
-        <v>6521837</v>
+        <v>6521909</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>endast läte</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120279002</v>
+        <v>120279000</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>90564</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,25 +1484,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4660</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,23 +1510,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292480</v>
+        <v>292494</v>
       </c>
       <c r="R9" t="n">
-        <v>6521807</v>
+        <v>6521833</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,17 +1567,13 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>massor av hack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1597,7 +1592,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120279012</v>
+        <v>120278950</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1632,22 +1627,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292451</v>
+        <v>292486</v>
       </c>
       <c r="R10" t="n">
-        <v>6521897</v>
+        <v>6521810</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1717,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120279004</v>
+        <v>120279026</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>90564</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,35 +1725,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>4660</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1765,13 +1760,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292460</v>
+        <v>292459</v>
       </c>
       <c r="R11" t="n">
-        <v>6521909</v>
+        <v>6521917</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,7 +1810,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>endast läte</t>
+          <t>Växer på döende Asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,8 +1819,9 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1842,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120278951</v>
+        <v>120279013</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,49 +1850,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292480</v>
+        <v>292553</v>
       </c>
       <c r="R12" t="n">
-        <v>6521806</v>
+        <v>6521837</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,7 +1931,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,7 +1945,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278936</v>
+        <v>120279010</v>
       </c>
       <c r="B13" t="n">
-        <v>90564</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,30 +1975,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292494</v>
+        <v>292451</v>
       </c>
       <c r="R13" t="n">
-        <v>6521833</v>
+        <v>6521897</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2041,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,7 +2056,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sönderhackad död gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,7 +2070,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2079,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120279026</v>
+        <v>120279012</v>
       </c>
       <c r="B14" t="n">
-        <v>90564</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,34 +2100,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2126,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292459</v>
+        <v>292451</v>
       </c>
       <c r="R14" t="n">
-        <v>6521917</v>
+        <v>6521897</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2161,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,12 +2180,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer på döende Asp</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,7 +2191,7 @@
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2204,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120278950</v>
+        <v>120279002</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,49 +2220,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292486</v>
+        <v>292480</v>
       </c>
       <c r="R15" t="n">
-        <v>6521810</v>
+        <v>6521807</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2287,7 +2291,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2301,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>massor av hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,7 +2315,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2325,10 +2333,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120279010</v>
+        <v>120278951</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,46 +2345,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292451</v>
+        <v>292480</v>
       </c>
       <c r="R16" t="n">
-        <v>6521897</v>
+        <v>6521806</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2408,7 +2416,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2418,12 +2426,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>sönderhackad död gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,6 +2435,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173739</v>
+        <v>120173772</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79583</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,35 +926,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,6 +1001,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120173772</v>
+        <v>120173739</v>
       </c>
       <c r="B5" t="n">
-        <v>79583</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,30 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1111,7 +1112,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120173709</v>
+        <v>120174574</v>
       </c>
       <c r="B6" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,31 +1142,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292402</v>
+        <v>292510</v>
       </c>
       <c r="R6" t="n">
-        <v>6521878</v>
+        <v>6521818</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,6 +1222,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120174574</v>
+        <v>120173709</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,35 +1253,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>292510</v>
+        <v>292402</v>
       </c>
       <c r="R7" t="n">
-        <v>6521818</v>
+        <v>6521878</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120279004</v>
+        <v>120278950</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,49 +1359,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292460</v>
+        <v>292486</v>
       </c>
       <c r="R8" t="n">
-        <v>6521909</v>
+        <v>6521810</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,12 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>endast läte</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,6 +1449,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120279000</v>
+        <v>120279012</v>
       </c>
       <c r="B9" t="n">
-        <v>90564</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,34 +1480,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1519,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292494</v>
+        <v>292451</v>
       </c>
       <c r="R9" t="n">
-        <v>6521833</v>
+        <v>6521897</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1554,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120278950</v>
+        <v>120279026</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>90564</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,46 +1600,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292486</v>
+        <v>292459</v>
       </c>
       <c r="R10" t="n">
-        <v>6521810</v>
+        <v>6521917</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1675,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1680,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer på döende Asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120279026</v>
+        <v>120279010</v>
       </c>
       <c r="B11" t="n">
-        <v>90564</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,34 +1725,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1760,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292459</v>
+        <v>292451</v>
       </c>
       <c r="R11" t="n">
-        <v>6521917</v>
+        <v>6521897</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1810,7 +1811,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växer på döende Asp</t>
+          <t>sönderhackad död gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,9 +1820,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1838,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120279013</v>
+        <v>120279002</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,16 +1854,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1882,14 +1882,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292553</v>
+        <v>292480</v>
       </c>
       <c r="R12" t="n">
-        <v>6521837</v>
+        <v>6521807</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>massor av hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120279010</v>
+        <v>120279013</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,16 +1979,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292451</v>
+        <v>292553</v>
       </c>
       <c r="R13" t="n">
-        <v>6521897</v>
+        <v>6521837</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sönderhackad död gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,7 +2088,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120279012</v>
+        <v>120278951</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2123,22 +2123,23 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292451</v>
+        <v>292480</v>
       </c>
       <c r="R14" t="n">
-        <v>6521897</v>
+        <v>6521806</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2208,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120279002</v>
+        <v>120279004</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,26 +2225,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2252,17 +2253,17 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292480</v>
+        <v>292460</v>
       </c>
       <c r="R15" t="n">
-        <v>6521807</v>
+        <v>6521909</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2291,7 +2292,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2301,12 +2302,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>massor av hack</t>
+          <t>endast läte</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2333,10 +2334,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120278951</v>
+        <v>120279000</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>90564</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2345,46 +2346,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292480</v>
+        <v>292494</v>
       </c>
       <c r="R16" t="n">
-        <v>6521806</v>
+        <v>6521833</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173772</v>
+        <v>120173709</v>
       </c>
       <c r="B4" t="n">
-        <v>79583</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,26 +930,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>292480</v>
+        <v>292402</v>
       </c>
       <c r="R4" t="n">
-        <v>6521913</v>
+        <v>6521878</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,7 +1002,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120173739</v>
+        <v>120174574</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>292480</v>
+        <v>292510</v>
       </c>
       <c r="R5" t="n">
-        <v>6521913</v>
+        <v>6521818</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120174574</v>
+        <v>120173739</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,35 +1143,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292510</v>
+        <v>292480</v>
       </c>
       <c r="R6" t="n">
-        <v>6521818</v>
+        <v>6521913</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,7 +1223,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173709</v>
+        <v>120173772</v>
       </c>
       <c r="B7" t="n">
-        <v>56532</v>
+        <v>79583</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,27 +1257,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>292402</v>
+        <v>292480</v>
       </c>
       <c r="R7" t="n">
-        <v>6521878</v>
+        <v>6521913</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,6 +1328,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120278950</v>
+        <v>120279000</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>90564</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,46 +1359,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292486</v>
+        <v>292494</v>
       </c>
       <c r="R8" t="n">
-        <v>6521810</v>
+        <v>6521833</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1430,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120279012</v>
+        <v>120279013</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,33 +1479,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1515,13 +1515,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292451</v>
+        <v>292553</v>
       </c>
       <c r="R9" t="n">
-        <v>6521897</v>
+        <v>6521837</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1560,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1574,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1588,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120279026</v>
+        <v>120279010</v>
       </c>
       <c r="B10" t="n">
-        <v>90564</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,34 +1604,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4660</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1635,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292459</v>
+        <v>292451</v>
       </c>
       <c r="R10" t="n">
-        <v>6521917</v>
+        <v>6521897</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1685,7 +1690,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på döende Asp</t>
+          <t>sönderhackad död gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,9 +1699,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1713,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120279010</v>
+        <v>120278951</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,46 +1729,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292451</v>
+        <v>292480</v>
       </c>
       <c r="R11" t="n">
-        <v>6521897</v>
+        <v>6521806</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1796,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,12 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>sönderhackad död gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,6 +1819,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120279002</v>
+        <v>120278950</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,49 +1850,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292480</v>
+        <v>292486</v>
       </c>
       <c r="R12" t="n">
-        <v>6521807</v>
+        <v>6521810</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,12 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>massor av hack</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,6 +1940,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1963,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120279013</v>
+        <v>120279002</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,16 +1975,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2007,14 +2003,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292553</v>
+        <v>292480</v>
       </c>
       <c r="R13" t="n">
-        <v>6521837</v>
+        <v>6521807</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2046,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,12 +2052,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>massor av hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120278951</v>
+        <v>120279004</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,49 +2096,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292480</v>
+        <v>292460</v>
       </c>
       <c r="R14" t="n">
-        <v>6521806</v>
+        <v>6521909</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2171,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2177,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>endast läte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,7 +2191,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120279004</v>
+        <v>120279026</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>90564</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,35 +2221,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4660</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2257,13 +2256,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292460</v>
+        <v>292459</v>
       </c>
       <c r="R15" t="n">
-        <v>6521909</v>
+        <v>6521917</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2307,7 +2306,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>endast läte</t>
+          <t>Växer på döende Asp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,8 +2315,9 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2334,10 +2334,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120279000</v>
+        <v>120279012</v>
       </c>
       <c r="B16" t="n">
-        <v>90564</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,34 +2346,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292494</v>
+        <v>292451</v>
       </c>
       <c r="R16" t="n">
-        <v>6521833</v>
+        <v>6521897</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120174574</v>
+        <v>120173739</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>292510</v>
+        <v>292480</v>
       </c>
       <c r="R5" t="n">
-        <v>6521818</v>
+        <v>6521913</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1112,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120173739</v>
+        <v>120174574</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,35 +1142,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1179,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292480</v>
+        <v>292510</v>
       </c>
       <c r="R6" t="n">
-        <v>6521913</v>
+        <v>6521818</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,6 +1222,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120279000</v>
+        <v>120278950</v>
       </c>
       <c r="B8" t="n">
-        <v>90564</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,45 +1359,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292494</v>
+        <v>292486</v>
       </c>
       <c r="R8" t="n">
-        <v>6521833</v>
+        <v>6521810</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1429,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120279013</v>
+        <v>120279004</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,26 +1484,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1515,13 +1516,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292553</v>
+        <v>292460</v>
       </c>
       <c r="R9" t="n">
-        <v>6521837</v>
+        <v>6521909</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,12 +1561,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>endast läte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120279010</v>
+        <v>120279012</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,34 +1605,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,12 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>sönderhackad död gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,6 +1694,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1717,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120278951</v>
+        <v>120279000</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>90564</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,46 +1725,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292480</v>
+        <v>292494</v>
       </c>
       <c r="R11" t="n">
-        <v>6521806</v>
+        <v>6521833</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1800,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1805,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120278950</v>
+        <v>120279002</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,49 +1845,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292486</v>
+        <v>292480</v>
       </c>
       <c r="R12" t="n">
-        <v>6521810</v>
+        <v>6521807</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +1916,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1926,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>massor av hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,7 +1940,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120279002</v>
+        <v>120279026</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>90564</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,49 +1970,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4660</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292480</v>
+        <v>292459</v>
       </c>
       <c r="R13" t="n">
-        <v>6521807</v>
+        <v>6521917</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2042,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,12 +2050,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>massor av hack</t>
+          <t>Växer på döende Asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,8 +2064,9 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2084,10 +2083,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120279004</v>
+        <v>120279010</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,26 +2099,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2132,13 +2131,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292460</v>
+        <v>292451</v>
       </c>
       <c r="R14" t="n">
-        <v>6521909</v>
+        <v>6521897</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2182,7 +2181,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>endast läte</t>
+          <t>sönderhackad död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120279026</v>
+        <v>120278951</v>
       </c>
       <c r="B15" t="n">
-        <v>90564</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,45 +2220,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292459</v>
+        <v>292480</v>
       </c>
       <c r="R15" t="n">
-        <v>6521917</v>
+        <v>6521806</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2301,12 +2301,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer på döende Asp</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2317,7 +2312,7 @@
       </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2334,10 +2329,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120279012</v>
+        <v>120279013</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2346,33 +2341,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2381,13 +2377,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292451</v>
+        <v>292553</v>
       </c>
       <c r="R16" t="n">
-        <v>6521897</v>
+        <v>6521837</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2416,7 +2412,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2426,7 +2422,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,7 +2436,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120173739</v>
+        <v>120174574</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>292480</v>
+        <v>292510</v>
       </c>
       <c r="R5" t="n">
-        <v>6521913</v>
+        <v>6521818</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120174574</v>
+        <v>120173772</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>79583</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,35 +1143,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292510</v>
+        <v>292480</v>
       </c>
       <c r="R6" t="n">
-        <v>6521818</v>
+        <v>6521913</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1241,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173772</v>
+        <v>120173739</v>
       </c>
       <c r="B7" t="n">
-        <v>79583</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,30 +1249,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1328,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120278950</v>
+        <v>120278936</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>90564</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,46 +1359,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292486</v>
+        <v>292494</v>
       </c>
       <c r="R8" t="n">
-        <v>6521810</v>
+        <v>6521833</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1468,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120279004</v>
+        <v>120279010</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,26 +1479,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1516,13 +1511,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292460</v>
+        <v>292451</v>
       </c>
       <c r="R9" t="n">
-        <v>6521909</v>
+        <v>6521897</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,7 +1561,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>endast läte</t>
+          <t>sönderhackad död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,7 +1588,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120279012</v>
+        <v>120278951</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1628,22 +1623,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292451</v>
+        <v>292480</v>
       </c>
       <c r="R10" t="n">
-        <v>6521897</v>
+        <v>6521806</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1713,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120279000</v>
+        <v>120279002</v>
       </c>
       <c r="B11" t="n">
-        <v>90564</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1751,22 +1747,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292494</v>
+        <v>292480</v>
       </c>
       <c r="R11" t="n">
-        <v>6521833</v>
+        <v>6521807</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,13 +1805,17 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>massor av hack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1833,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120279002</v>
+        <v>120279013</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,16 +1850,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1877,14 +1878,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292480</v>
+        <v>292553</v>
       </c>
       <c r="R12" t="n">
-        <v>6521807</v>
+        <v>6521837</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1916,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1926,12 +1927,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>massor av hack</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120279026</v>
+        <v>120279004</v>
       </c>
       <c r="B13" t="n">
-        <v>90564</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,34 +1971,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2005,13 +2007,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292459</v>
+        <v>292460</v>
       </c>
       <c r="R13" t="n">
-        <v>6521917</v>
+        <v>6521909</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,7 +2057,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer på döende Asp</t>
+          <t>endast läte</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,9 +2066,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2083,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120279010</v>
+        <v>120278950</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,46 +2096,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Mårtensröd, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292451</v>
+        <v>292486</v>
       </c>
       <c r="R14" t="n">
-        <v>6521897</v>
+        <v>6521810</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2166,7 +2167,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,12 +2177,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>sönderhackad död gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,6 +2186,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2208,7 +2205,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120278951</v>
+        <v>120279012</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2243,23 +2240,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292480</v>
+        <v>292451</v>
       </c>
       <c r="R15" t="n">
-        <v>6521806</v>
+        <v>6521897</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2329,10 +2325,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120279013</v>
+        <v>120279026</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>90564</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,35 +2337,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2377,13 +2372,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292553</v>
+        <v>292459</v>
       </c>
       <c r="R16" t="n">
-        <v>6521837</v>
+        <v>6521917</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2412,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2422,12 +2417,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Växer på döende Asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,8 +2431,9 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119764981</v>
+        <v>120279020</v>
       </c>
       <c r="B2" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mannemyr, Mannemyr, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>292408</v>
+        <v>292502</v>
       </c>
       <c r="R2" t="n">
-        <v>6521923</v>
+        <v>6521924</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,27 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillning och flyktbrak ca 20 m</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,18 +772,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -800,12 +794,7 @@
         <v>119871405</v>
       </c>
       <c r="B3" t="n">
-        <v>96198</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120173772</v>
+        <v>120278936</v>
       </c>
       <c r="B4" t="n">
-        <v>79583</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,17 +937,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Amundshatt, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>292480</v>
+        <v>292494</v>
       </c>
       <c r="R4" t="n">
-        <v>6521913</v>
+        <v>6521833</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,12 +971,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,73 +1002,67 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120174574</v>
+        <v>120279026</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Amundshatt, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>292510</v>
+        <v>292459</v>
       </c>
       <c r="R5" t="n">
-        <v>6521818</v>
+        <v>6521917</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,12 +1086,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på döende Asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,49 +1117,44 @@
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120173739</v>
+        <v>120173783</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1169,7 +1167,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1179,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>292480</v>
+        <v>292501</v>
       </c>
       <c r="R6" t="n">
-        <v>6521913</v>
+        <v>6521928</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1241,15 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120173709</v>
+        <v>120279002</v>
       </c>
       <c r="B7" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,38 +1250,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Amundshatt, Boh</t>
+          <t>amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>292402</v>
+        <v>292480</v>
       </c>
       <c r="R7" t="n">
-        <v>6521878</v>
+        <v>6521807</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,12 +1312,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>massor av hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1347,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120279000</v>
+        <v>120279010</v>
       </c>
       <c r="B8" t="n">
-        <v>90616</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1370,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,8 +1392,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292494</v>
+        <v>292451</v>
       </c>
       <c r="R8" t="n">
-        <v>6521833</v>
+        <v>6521897</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1429,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>sönderhackad död gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,7 +1461,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1467,60 +1479,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120279012</v>
+        <v>120173717</v>
       </c>
       <c r="B9" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Amundshatt, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292451</v>
+        <v>292463</v>
       </c>
       <c r="R9" t="n">
-        <v>6521897</v>
+        <v>6521894</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,22 +1552,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,34 +1566,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120279010</v>
+        <v>120173739</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1603,16 +1595,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1620,28 +1612,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Amundshatt, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292451</v>
+        <v>292480</v>
       </c>
       <c r="R10" t="n">
-        <v>6521897</v>
+        <v>6521913</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,27 +1657,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>sönderhackad död gran</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,72 +1677,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120279026</v>
+        <v>120174531</v>
       </c>
       <c r="B11" t="n">
-        <v>90616</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Amunderöd, Boh</t>
+          <t>Amundshatt, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292459</v>
+        <v>292567</v>
       </c>
       <c r="R11" t="n">
-        <v>6521917</v>
+        <v>6521839</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1789,27 +1762,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer på döende Asp</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,34 +1776,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120279004</v>
+        <v>120278996</v>
       </c>
       <c r="B12" t="n">
-        <v>57485</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,26 +1805,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1885,13 +1837,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292460</v>
+        <v>292522</v>
       </c>
       <c r="R12" t="n">
-        <v>6521909</v>
+        <v>6521792</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,12 +1882,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>endast läte</t>
+          <t>ringhack tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,61 +1914,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120278951</v>
+        <v>120279013</v>
       </c>
       <c r="B13" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292480</v>
+        <v>292553</v>
       </c>
       <c r="R13" t="n">
-        <v>6521806</v>
+        <v>6521837</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2045,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +2002,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,7 +2016,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2083,15 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120279013</v>
+        <v>120279024</v>
       </c>
       <c r="B14" t="n">
-        <v>57332</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292553</v>
+        <v>292477</v>
       </c>
       <c r="R14" t="n">
-        <v>6521837</v>
+        <v>6521900</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2166,7 +2112,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,12 +2122,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Bohåli en tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,61 +2154,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120278950</v>
+        <v>101123300</v>
       </c>
       <c r="B15" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mårtensröd, Boh</t>
+          <t>Amunderöd-Ranebo, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>292486</v>
       </c>
       <c r="R15" t="n">
-        <v>6521810</v>
+        <v>6521852</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2286,22 +2223,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,80 +2237,71 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120279002</v>
+        <v>119764981</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>amunderöd, Boh</t>
+          <t>Mannemyr, Mannemyr, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292480</v>
+        <v>292408</v>
       </c>
       <c r="R16" t="n">
-        <v>6521807</v>
+        <v>6521923</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2407,27 +2325,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>massor av hack</t>
+          <t>Spillning och flyktbrak ca 20 m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,15 +2360,1214 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119765760</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mannemyr, Mannemyr, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>292370</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6521899</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120173709</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>292402</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6521878</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>101123229</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Amunderöd-Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>292570</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6521848</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120279004</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Amunderöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>292460</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6521909</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>endast läte</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Erland Svenson</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Erland Svenson</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>101123230</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Amunderöd-Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>292570</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6521848</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120174574</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>292510</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6521818</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120278950</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mårtensröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>292486</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6521810</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120278951</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mårtensröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>292480</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6521806</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120279012</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Amunderöd, Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>292451</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6521897</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120173772</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>292480</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6521913</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120174535</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>292567</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6521839</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279020</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278936</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120173783</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279002</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279010</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120173717</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1686,6 +1731,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120173739</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,6 +1841,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120174531</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1911,6 +1966,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278996</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2031,6 +2091,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279013</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2151,6 +2216,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279024</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2252,6 +2322,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101123300</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2369,6 +2444,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119764981</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2486,6 +2566,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119765760</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2587,6 +2672,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120173709</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2690,6 +2780,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101123229</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2810,6 +2905,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279004</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2913,6 +3013,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101123230</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3019,6 +3124,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120174574</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3245,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278950</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3251,6 +3366,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120278951</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3366,6 +3486,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120279012</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3467,6 +3592,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120173772</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3568,8 +3698,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120174535</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>